--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:34:41+00:00</t>
+    <t>2026-09-17T13:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:31:08+00:00</t>
+    <t>2026-10-12T16:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
